--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/05_Lizenz_Forderungen/04_Offene_Posten_Lizenzen.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/05_Lizenz_Forderungen/04_Offene_Posten_Lizenzen.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Posten" sheetId="1" r:id="Re68ecb535d66477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="2" r:id="R4d35e39057754403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzungen" sheetId="3" r:id="R87d501f4ccc64064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Posten" sheetId="1" r:id="Rd49bb34ddf4946c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="2" r:id="Rb7053d0a203a457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzungen" sheetId="3" r:id="R72b1a751deae4125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventar_Ueberleitung" sheetId="4" r:id="R4b55f5b790e64b8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -848,4 +849,110 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Offene Lizenz- und Vertriebsforderungen</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="4"/>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Arbeitsstand aus den beigefügten Aktenstücken; offene Angaben bleiben offen und sind nicht als Nullwert zu behandeln. Die Überleitung ersetzt die frühere, nicht abgestimmte Arbeitssumme von 321.628 EUR.</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Position</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Betrag EUR</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Berechnung/Einordnung</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="14" t="str">
+        <x:v>Bruttolistenwert aller sechs Zeilen</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:f>SUM(Offene_Posten!$E$6:$E$11)</x:f>
+        <x:v>302728</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>302.728 EUR einschließlich bereits bezahlter Rheinbild-Rate KL-2026-119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>abzüglich bezahlte Rheinbild-Rate KL-2026-119</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="n">
+        <x:v>-107100</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>Zahlung 06.04.2026 auf operatives Konto</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="14" t="str">
+        <x:v>nominell offen oder zukünftig</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:f>B6+B7</x:f>
+        <x:v>195628</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>195.628 EUR; Teilzahlung und Einwendungen gesondert prüfen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="15" t="str">
+        <x:v>technische Nachvergütung Rheinbild</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="n">
+        <x:v>17850</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="str">
+        <x:v>Zahlung 06.10.2026 auf Massekonto; nicht Bestandteil der sechs Bruttolistenzeilen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="A10" s="14" t="str">
+        <x:v>Kontrolle Inventarvermerk</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:f>B8-195628</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>muss 0 ergeben</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C2"/>
+    <x:mergeCell ref="A3:C3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/05_Lizenz_Forderungen/04_Offene_Posten_Lizenzen.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/05_Lizenz_Forderungen/04_Offene_Posten_Lizenzen.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Posten" sheetId="1" r:id="Rd49bb34ddf4946c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="2" r:id="Rb7053d0a203a457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzungen" sheetId="3" r:id="R72b1a751deae4125"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventar_Ueberleitung" sheetId="4" r:id="R4b55f5b790e64b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Posten" sheetId="1" r:id="Rc8a0c3d53bf64db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="2" r:id="R6211f07516d84ae9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzungen" sheetId="3" r:id="R526af12109d74548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventar_Ueberleitung" sheetId="4" r:id="R59c49d5401474b2c"/>
   </x:sheets>
 </x:workbook>
 </file>
